--- a/DTT-Assessment-Hour-Log.xlsx
+++ b/DTT-Assessment-Hour-Log.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bae1ac55f5db4960/Desktop/DTT_assessment/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\dtt-frontend-assessment\dtt-frontend-assessment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="33" documentId="8_{49F91033-96F3-7148-A020-201798871A5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BF858867-1A1D-45F4-9E64-E6575D8DC05A}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6D68B41-DA8C-4C9E-9D96-22C4924DD0A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19125" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="28800" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DTT Test Hour Log" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
   <si>
     <t>Subject</t>
   </si>
@@ -111,6 +111,12 @@
   <si>
     <t>18/05/2026</t>
   </si>
+  <si>
+    <t>Assets setup</t>
+  </si>
+  <si>
+    <t>Added DTT provided icons and images to src/assets folder, organized into icons and images subfolders</t>
+  </si>
 </sst>
 </file>
 
@@ -118,7 +124,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy;@"/>
-    <numFmt numFmtId="167" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
   <fonts count="12" x14ac:knownFonts="1">
     <font>
@@ -450,6 +456,12 @@
     <xf numFmtId="49" fontId="11" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="1" fontId="1" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -461,12 +473,6 @@
     </xf>
     <xf numFmtId="1" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="3" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="167" fontId="3" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1737,22 +1743,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="73.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="20"/>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
+      <c r="A1" s="22"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
       <c r="E1" s="10"/>
       <c r="F1" s="2"/>
     </row>
     <row r="2" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="23"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="25"/>
     </row>
     <row r="3" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="16" t="s">
@@ -1776,7 +1782,7 @@
       <c r="A4" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="25">
+      <c r="B4" s="21">
         <v>0.5</v>
       </c>
       <c r="C4" s="17" t="s">
@@ -1792,7 +1798,7 @@
       <c r="A5" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="25">
+      <c r="B5" s="21">
         <v>1</v>
       </c>
       <c r="C5" s="17" t="s">
@@ -1808,7 +1814,7 @@
       <c r="A6" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="25">
+      <c r="B6" s="21">
         <v>0.5</v>
       </c>
       <c r="C6" s="17" t="s">
@@ -1824,7 +1830,7 @@
       <c r="A7" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="25">
+      <c r="B7" s="21">
         <v>0.5</v>
       </c>
       <c r="C7" s="17" t="s">
@@ -1840,7 +1846,7 @@
       <c r="A8" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="25">
+      <c r="B8" s="21">
         <v>0.5</v>
       </c>
       <c r="C8" s="17" t="s">
@@ -1853,24 +1859,32 @@
       <c r="F8" s="4"/>
     </row>
     <row r="9" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="5"/>
-      <c r="B9" s="25"/>
-      <c r="C9" s="17"/>
-      <c r="D9" s="15"/>
+      <c r="A9" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="21">
+        <v>0.5</v>
+      </c>
+      <c r="C9" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>20</v>
+      </c>
       <c r="E9" s="19"/>
       <c r="F9" s="4"/>
     </row>
     <row r="10" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="5"/>
-      <c r="B10" s="25"/>
+      <c r="B10" s="21"/>
       <c r="C10" s="17"/>
-      <c r="D10" s="24"/>
+      <c r="D10" s="20"/>
       <c r="E10" s="19"/>
       <c r="F10" s="4"/>
     </row>
     <row r="11" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="5"/>
-      <c r="B11" s="25"/>
+      <c r="B11" s="21"/>
       <c r="C11" s="17"/>
       <c r="D11" s="15"/>
       <c r="E11" s="19"/>
@@ -1878,7 +1892,7 @@
     </row>
     <row r="12" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="5"/>
-      <c r="B12" s="25"/>
+      <c r="B12" s="21"/>
       <c r="C12" s="17"/>
       <c r="D12" s="15"/>
       <c r="E12" s="19"/>
@@ -1886,7 +1900,7 @@
     </row>
     <row r="13" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="5"/>
-      <c r="B13" s="25"/>
+      <c r="B13" s="21"/>
       <c r="C13" s="17"/>
       <c r="D13" s="15"/>
       <c r="E13" s="19"/>
@@ -1894,7 +1908,7 @@
     </row>
     <row r="14" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="5"/>
-      <c r="B14" s="25"/>
+      <c r="B14" s="21"/>
       <c r="C14" s="17"/>
       <c r="D14" s="15"/>
       <c r="E14" s="19"/>
@@ -1902,7 +1916,7 @@
     </row>
     <row r="15" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="5"/>
-      <c r="B15" s="25"/>
+      <c r="B15" s="21"/>
       <c r="C15" s="17"/>
       <c r="D15" s="15"/>
       <c r="E15" s="19"/>
@@ -1910,7 +1924,7 @@
     </row>
     <row r="16" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="5"/>
-      <c r="B16" s="25"/>
+      <c r="B16" s="21"/>
       <c r="C16" s="17"/>
       <c r="D16" s="15"/>
       <c r="E16" s="19"/>
@@ -1918,7 +1932,7 @@
     </row>
     <row r="17" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="5"/>
-      <c r="B17" s="25"/>
+      <c r="B17" s="21"/>
       <c r="C17" s="17"/>
       <c r="D17" s="15"/>
       <c r="E17" s="19"/>
@@ -1926,7 +1940,7 @@
     </row>
     <row r="18" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="5"/>
-      <c r="B18" s="25"/>
+      <c r="B18" s="21"/>
       <c r="C18" s="17"/>
       <c r="D18" s="15"/>
       <c r="E18" s="19"/>
@@ -1934,7 +1948,7 @@
     </row>
     <row r="19" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="5"/>
-      <c r="B19" s="25"/>
+      <c r="B19" s="21"/>
       <c r="C19" s="17"/>
       <c r="D19" s="15"/>
       <c r="E19" s="19"/>
@@ -1942,7 +1956,7 @@
     </row>
     <row r="20" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="5"/>
-      <c r="B20" s="25"/>
+      <c r="B20" s="21"/>
       <c r="C20" s="17"/>
       <c r="D20" s="15"/>
       <c r="E20" s="19"/>
@@ -1950,7 +1964,7 @@
     </row>
     <row r="21" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="5"/>
-      <c r="B21" s="25"/>
+      <c r="B21" s="21"/>
       <c r="C21" s="17"/>
       <c r="D21" s="15"/>
       <c r="E21" s="19"/>
@@ -1958,7 +1972,7 @@
     </row>
     <row r="22" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="5"/>
-      <c r="B22" s="25"/>
+      <c r="B22" s="21"/>
       <c r="C22" s="17"/>
       <c r="D22" s="15"/>
       <c r="E22" s="19"/>
@@ -1966,7 +1980,7 @@
     </row>
     <row r="23" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="5"/>
-      <c r="B23" s="25"/>
+      <c r="B23" s="21"/>
       <c r="C23" s="17"/>
       <c r="D23" s="15"/>
       <c r="E23" s="19"/>
@@ -1974,7 +1988,7 @@
     </row>
     <row r="24" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="5"/>
-      <c r="B24" s="25"/>
+      <c r="B24" s="21"/>
       <c r="C24" s="17"/>
       <c r="D24" s="15"/>
       <c r="E24" s="19"/>
@@ -1982,7 +1996,7 @@
     </row>
     <row r="25" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="5"/>
-      <c r="B25" s="25"/>
+      <c r="B25" s="21"/>
       <c r="C25" s="17"/>
       <c r="D25" s="15"/>
       <c r="E25" s="19"/>
@@ -1990,7 +2004,7 @@
     </row>
     <row r="26" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="5"/>
-      <c r="B26" s="25"/>
+      <c r="B26" s="21"/>
       <c r="C26" s="17"/>
       <c r="D26" s="15"/>
       <c r="E26" s="19"/>
@@ -1998,7 +2012,7 @@
     </row>
     <row r="27" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="5"/>
-      <c r="B27" s="25"/>
+      <c r="B27" s="21"/>
       <c r="C27" s="17"/>
       <c r="D27" s="15"/>
       <c r="E27" s="19"/>
@@ -2006,7 +2020,7 @@
     </row>
     <row r="28" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="5"/>
-      <c r="B28" s="25"/>
+      <c r="B28" s="21"/>
       <c r="C28" s="17"/>
       <c r="D28" s="15"/>
       <c r="E28" s="19"/>
@@ -2026,7 +2040,7 @@
       </c>
       <c r="B30" s="14">
         <f>SUMIF(E4:E28,"&lt;&gt;x",B4:B28)</f>
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>

--- a/DTT-Assessment-Hour-Log.xlsx
+++ b/DTT-Assessment-Hour-Log.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\dtt-frontend-assessment\dtt-frontend-assessment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6D68B41-DA8C-4C9E-9D96-22C4924DD0A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EEE7105-1AA0-4665-8519-2BEDAB25EB20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="2340" windowWidth="28800" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DTT Test Hour Log" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="25">
   <si>
     <t>Subject</t>
   </si>
@@ -116,6 +116,18 @@
   </si>
   <si>
     <t>Added DTT provided icons and images to src/assets folder, organized into icons and images subfolders</t>
+  </si>
+  <si>
+    <t>Resolved accidental .env commit by removing file from Git tracking and rewriting Git history using filter-branch to eliminate exposed API key from all previous commits</t>
+  </si>
+  <si>
+    <t>Pinia store</t>
+  </si>
+  <si>
+    <t>Created houses Pinia store as single source of truth for house data. Implemented state, getters for sorting by price and size and actions for fetching all houses fetching single house by ID and deleting a house with error handling</t>
+  </si>
+  <si>
+    <t>23/05/2026</t>
   </si>
 </sst>
 </file>
@@ -1737,7 +1749,7 @@
     <col min="1" max="1" width="24.69921875" style="1" customWidth="1"/>
     <col min="2" max="2" width="10.69921875" style="1" customWidth="1"/>
     <col min="3" max="3" width="8.59765625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="58.296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="158.09765625" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="6.5" style="1" customWidth="1"/>
     <col min="7" max="251" width="6.5" customWidth="1"/>
   </cols>
@@ -1874,19 +1886,35 @@
       <c r="E9" s="19"/>
       <c r="F9" s="4"/>
     </row>
-    <row r="10" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="5"/>
-      <c r="B10" s="21"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="20"/>
+    <row r="10" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+      <c r="A10" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="21">
+        <v>0.5</v>
+      </c>
+      <c r="C10" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="20" t="s">
+        <v>21</v>
+      </c>
       <c r="E10" s="19"/>
       <c r="F10" s="4"/>
     </row>
-    <row r="11" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="5"/>
-      <c r="B11" s="21"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="15"/>
+    <row r="11" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+      <c r="A11" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="21">
+        <v>1.5</v>
+      </c>
+      <c r="C11" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>23</v>
+      </c>
       <c r="E11" s="19"/>
       <c r="F11" s="4"/>
     </row>
@@ -2040,7 +2068,7 @@
       </c>
       <c r="B30" s="14">
         <f>SUMIF(E4:E28,"&lt;&gt;x",B4:B28)</f>
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>

--- a/DTT-Assessment-Hour-Log.xlsx
+++ b/DTT-Assessment-Hour-Log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\dtt-frontend-assessment\dtt-frontend-assessment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EEE7105-1AA0-4665-8519-2BEDAB25EB20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10DC583E-BE48-41E5-B5C7-236BFED47DFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="34">
   <si>
     <t>Subject</t>
   </si>
@@ -128,6 +128,33 @@
   </si>
   <si>
     <t>23/05/2026</t>
+  </si>
+  <si>
+    <t>Global CSS variables</t>
+  </si>
+  <si>
+    <t>NavBar component</t>
+  </si>
+  <si>
+    <t>NavBar styling</t>
+  </si>
+  <si>
+    <t>24/05/2026</t>
+  </si>
+  <si>
+    <t>Created global CSS variables file with all design tokens from DTT styleguide including colors, typography, spacing and border radius. Used CSS variables throughout all components instead of hardcoded values for maintainability and consistency</t>
+  </si>
+  <si>
+    <t>Built NavBar component with DTT logo and navigation links to Houses and About pages. Implemented active route highlighting using Vue Router's $route. Resolved import issues with useRoute by switching to globally available $route instead</t>
+  </si>
+  <si>
+    <t>Styled NavBar to match DTT styleguide design. Added responsive padding using clamp() to correct appearance across different screen sizes. Applied CSS variables for all style properties instead of hardcoded values</t>
+  </si>
+  <si>
+    <t>App.vue setup</t>
+  </si>
+  <si>
+    <t>Updated App.vue to include NavBar component and RouterView. NavBar is displayed on all pages while RouterView renders the current page based on the URL</t>
   </si>
 </sst>
 </file>
@@ -1744,17 +1771,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F33"/>
-  <sheetFormatPr defaultColWidth="6.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="6.46484375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.69921875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="10.69921875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="24.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="10.6640625" style="1" customWidth="1"/>
     <col min="3" max="3" width="8.59765625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="158.09765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="6.5" style="1" customWidth="1"/>
-    <col min="7" max="251" width="6.5" customWidth="1"/>
+    <col min="4" max="4" width="158.06640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="6.46484375" style="1" customWidth="1"/>
+    <col min="7" max="251" width="6.46484375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="73.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="73.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="22"/>
       <c r="B1" s="23"/>
       <c r="C1" s="23"/>
@@ -1762,7 +1789,7 @@
       <c r="E1" s="10"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="24" t="s">
         <v>6</v>
       </c>
@@ -1772,7 +1799,7 @@
       <c r="E2" s="24"/>
       <c r="F2" s="25"/>
     </row>
-    <row r="3" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="16" t="s">
         <v>0</v>
       </c>
@@ -1790,7 +1817,7 @@
       </c>
       <c r="F3" s="4"/>
     </row>
-    <row r="4" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A4" s="5" t="s">
         <v>7</v>
       </c>
@@ -1806,7 +1833,7 @@
       <c r="E4" s="19"/>
       <c r="F4" s="4"/>
     </row>
-    <row r="5" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" ht="18" x14ac:dyDescent="0.5">
       <c r="A5" s="5" t="s">
         <v>9</v>
       </c>
@@ -1822,7 +1849,7 @@
       <c r="E5" s="19"/>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A6" s="18" t="s">
         <v>12</v>
       </c>
@@ -1838,7 +1865,7 @@
       <c r="E6" s="19"/>
       <c r="F6" s="4"/>
     </row>
-    <row r="7" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A7" s="5" t="s">
         <v>14</v>
       </c>
@@ -1854,7 +1881,7 @@
       <c r="E7" s="19"/>
       <c r="F7" s="4"/>
     </row>
-    <row r="8" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A8" s="5" t="s">
         <v>16</v>
       </c>
@@ -1870,7 +1897,7 @@
       <c r="E8" s="19"/>
       <c r="F8" s="4"/>
     </row>
-    <row r="9" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A9" s="5" t="s">
         <v>19</v>
       </c>
@@ -1886,7 +1913,7 @@
       <c r="E9" s="19"/>
       <c r="F9" s="4"/>
     </row>
-    <row r="10" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" ht="18" x14ac:dyDescent="0.5">
       <c r="A10" s="5" t="s">
         <v>16</v>
       </c>
@@ -1902,7 +1929,7 @@
       <c r="E10" s="19"/>
       <c r="F10" s="4"/>
     </row>
-    <row r="11" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" ht="18" x14ac:dyDescent="0.5">
       <c r="A11" s="5" t="s">
         <v>22</v>
       </c>
@@ -1918,39 +1945,71 @@
       <c r="E11" s="19"/>
       <c r="F11" s="4"/>
     </row>
-    <row r="12" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="5"/>
-      <c r="B12" s="21"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="15"/>
+    <row r="12" spans="1:6" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A12" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="21">
+        <v>0.5</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>29</v>
+      </c>
       <c r="E12" s="19"/>
       <c r="F12" s="4"/>
     </row>
-    <row r="13" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="5"/>
-      <c r="B13" s="21"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="15"/>
+    <row r="13" spans="1:6" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A13" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="21">
+        <v>1</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>30</v>
+      </c>
       <c r="E13" s="19"/>
       <c r="F13" s="4"/>
     </row>
-    <row r="14" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="5"/>
-      <c r="B14" s="21"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="15"/>
+    <row r="14" spans="1:6" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A14" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" s="21">
+        <v>0.5</v>
+      </c>
+      <c r="C14" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="D14" s="15" t="s">
+        <v>31</v>
+      </c>
       <c r="E14" s="19"/>
       <c r="F14" s="4"/>
     </row>
-    <row r="15" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="5"/>
-      <c r="B15" s="21"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="15"/>
+    <row r="15" spans="1:6" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A15" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" s="21">
+        <v>0.5</v>
+      </c>
+      <c r="C15" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="D15" s="15" t="s">
+        <v>33</v>
+      </c>
       <c r="E15" s="19"/>
       <c r="F15" s="4"/>
     </row>
-    <row r="16" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A16" s="5"/>
       <c r="B16" s="21"/>
       <c r="C16" s="17"/>
@@ -1958,7 +2017,7 @@
       <c r="E16" s="19"/>
       <c r="F16" s="4"/>
     </row>
-    <row r="17" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A17" s="5"/>
       <c r="B17" s="21"/>
       <c r="C17" s="17"/>
@@ -1966,7 +2025,7 @@
       <c r="E17" s="19"/>
       <c r="F17" s="4"/>
     </row>
-    <row r="18" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A18" s="5"/>
       <c r="B18" s="21"/>
       <c r="C18" s="17"/>
@@ -1974,7 +2033,7 @@
       <c r="E18" s="19"/>
       <c r="F18" s="4"/>
     </row>
-    <row r="19" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A19" s="5"/>
       <c r="B19" s="21"/>
       <c r="C19" s="17"/>
@@ -1982,7 +2041,7 @@
       <c r="E19" s="19"/>
       <c r="F19" s="4"/>
     </row>
-    <row r="20" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A20" s="5"/>
       <c r="B20" s="21"/>
       <c r="C20" s="17"/>
@@ -1990,7 +2049,7 @@
       <c r="E20" s="19"/>
       <c r="F20" s="4"/>
     </row>
-    <row r="21" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A21" s="5"/>
       <c r="B21" s="21"/>
       <c r="C21" s="17"/>
@@ -1998,7 +2057,7 @@
       <c r="E21" s="19"/>
       <c r="F21" s="4"/>
     </row>
-    <row r="22" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A22" s="5"/>
       <c r="B22" s="21"/>
       <c r="C22" s="17"/>
@@ -2006,7 +2065,7 @@
       <c r="E22" s="19"/>
       <c r="F22" s="4"/>
     </row>
-    <row r="23" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A23" s="5"/>
       <c r="B23" s="21"/>
       <c r="C23" s="17"/>
@@ -2014,7 +2073,7 @@
       <c r="E23" s="19"/>
       <c r="F23" s="4"/>
     </row>
-    <row r="24" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A24" s="5"/>
       <c r="B24" s="21"/>
       <c r="C24" s="17"/>
@@ -2022,7 +2081,7 @@
       <c r="E24" s="19"/>
       <c r="F24" s="4"/>
     </row>
-    <row r="25" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A25" s="5"/>
       <c r="B25" s="21"/>
       <c r="C25" s="17"/>
@@ -2030,7 +2089,7 @@
       <c r="E25" s="19"/>
       <c r="F25" s="4"/>
     </row>
-    <row r="26" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A26" s="5"/>
       <c r="B26" s="21"/>
       <c r="C26" s="17"/>
@@ -2038,7 +2097,7 @@
       <c r="E26" s="19"/>
       <c r="F26" s="4"/>
     </row>
-    <row r="27" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A27" s="5"/>
       <c r="B27" s="21"/>
       <c r="C27" s="17"/>
@@ -2046,7 +2105,7 @@
       <c r="E27" s="19"/>
       <c r="F27" s="4"/>
     </row>
-    <row r="28" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:6" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A28" s="5"/>
       <c r="B28" s="21"/>
       <c r="C28" s="17"/>
@@ -2054,7 +2113,7 @@
       <c r="E28" s="19"/>
       <c r="F28" s="4"/>
     </row>
-    <row r="29" spans="1:6" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="11"/>
       <c r="B29" s="12"/>
       <c r="C29" s="12"/>
@@ -2062,20 +2121,20 @@
       <c r="E29" s="3"/>
       <c r="F29" s="4"/>
     </row>
-    <row r="30" spans="1:6" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="13" t="s">
         <v>4</v>
       </c>
       <c r="B30" s="14">
         <f>SUMIF(E4:E28,"&lt;&gt;x",B4:B28)</f>
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
       <c r="E30" s="3"/>
       <c r="F30" s="4"/>
     </row>
-    <row r="31" spans="1:6" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="6"/>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
@@ -2083,7 +2142,7 @@
       <c r="E31" s="3"/>
       <c r="F31" s="4"/>
     </row>
-    <row r="32" spans="1:6" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="6"/>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
@@ -2091,7 +2150,7 @@
       <c r="E32" s="3"/>
       <c r="F32" s="4"/>
     </row>
-    <row r="33" spans="1:6" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="7"/>
       <c r="B33" s="8"/>
       <c r="C33" s="8"/>

--- a/DTT-Assessment-Hour-Log.xlsx
+++ b/DTT-Assessment-Hour-Log.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\dtt-frontend-assessment\dtt-frontend-assessment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10DC583E-BE48-41E5-B5C7-236BFED47DFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A20F80F-2256-42E3-A960-D51520064F6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="50" windowWidth="25600" windowHeight="15230" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DTT Test Hour Log" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="43">
   <si>
     <t>Subject</t>
   </si>
@@ -155,6 +155,33 @@
   </si>
   <si>
     <t>Updated App.vue to include NavBar component and RouterView. NavBar is displayed on all pages while RouterView renders the current page based on the URL</t>
+  </si>
+  <si>
+    <t>HouseCard component</t>
+  </si>
+  <si>
+    <t>Built reusable HouseCard component displaying house image, address, price, postal code, city, bedrooms, bathrooms and size with icons. Used CSS variables throughout for consistent styling</t>
+  </si>
+  <si>
+    <t>Houses overview</t>
+  </si>
+  <si>
+    <t>Built HousesView page fetching and displaying all house listings from DTT API via Pinia store. Implemented search filtering by street, city, zip and price using computed property</t>
+  </si>
+  <si>
+    <t>Search and sort</t>
+  </si>
+  <si>
+    <t>25/05/2026</t>
+  </si>
+  <si>
+    <t>Added sort functionality by price and size using computed properties. Added search results count and empty state message when no results are found</t>
+  </si>
+  <si>
+    <t>HousesView styling</t>
+  </si>
+  <si>
+    <t>Styled houses overview page to match DTT styleguide. Applied CSS variables for all colors, typography and spacing. Added responsive padding using clamp()</t>
   </si>
 </sst>
 </file>
@@ -1953,7 +1980,7 @@
         <v>0.5</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D12" s="15" t="s">
         <v>29</v>
@@ -1969,7 +1996,7 @@
         <v>1</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D13" s="15" t="s">
         <v>30</v>
@@ -2010,34 +2037,66 @@
       <c r="F15" s="4"/>
     </row>
     <row r="16" spans="1:6" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A16" s="5"/>
-      <c r="B16" s="21"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="15"/>
+      <c r="A16" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16" s="21">
+        <v>1</v>
+      </c>
+      <c r="C16" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="D16" s="15" t="s">
+        <v>35</v>
+      </c>
       <c r="E16" s="19"/>
       <c r="F16" s="4"/>
     </row>
     <row r="17" spans="1:6" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A17" s="5"/>
-      <c r="B17" s="21"/>
-      <c r="C17" s="17"/>
-      <c r="D17" s="15"/>
+      <c r="A17" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B17" s="21">
+        <v>1.5</v>
+      </c>
+      <c r="C17" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="D17" s="15" t="s">
+        <v>37</v>
+      </c>
       <c r="E17" s="19"/>
       <c r="F17" s="4"/>
     </row>
     <row r="18" spans="1:6" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A18" s="5"/>
-      <c r="B18" s="21"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="15"/>
+      <c r="A18" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="21">
+        <v>1</v>
+      </c>
+      <c r="C18" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="D18" s="15" t="s">
+        <v>40</v>
+      </c>
       <c r="E18" s="19"/>
       <c r="F18" s="4"/>
     </row>
     <row r="19" spans="1:6" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A19" s="5"/>
-      <c r="B19" s="21"/>
-      <c r="C19" s="17"/>
-      <c r="D19" s="15"/>
+      <c r="A19" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B19" s="21">
+        <v>1</v>
+      </c>
+      <c r="C19" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="D19" s="15" t="s">
+        <v>42</v>
+      </c>
       <c r="E19" s="19"/>
       <c r="F19" s="4"/>
     </row>
@@ -2127,7 +2186,7 @@
       </c>
       <c r="B30" s="14">
         <f>SUMIF(E4:E28,"&lt;&gt;x",B4:B28)</f>
-        <v>8</v>
+        <v>12.5</v>
       </c>
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>

--- a/DTT-Assessment-Hour-Log.xlsx
+++ b/DTT-Assessment-Hour-Log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\dtt-frontend-assessment\dtt-frontend-assessment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A20F80F-2256-42E3-A960-D51520064F6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CCB0B30-DE9E-451E-9F1B-54C054A04679}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="50" windowWidth="25600" windowHeight="15230" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="45">
   <si>
     <t>Subject</t>
   </si>
@@ -182,6 +182,12 @@
   </si>
   <si>
     <t>Styled houses overview page to match DTT styleguide. Applied CSS variables for all colors, typography and spacing. Added responsive padding using clamp()</t>
+  </si>
+  <si>
+    <t>HouseCard hover actions</t>
+  </si>
+  <si>
+    <t>Added edit and delete action buttons to HouseCard component that appear on hover. Buttons are only visible for owned listings using madeByMe property from the API. Used opacity transition for smooth hover effect. Delete emits event to parent, edit navigates to edit page</t>
   </si>
 </sst>
 </file>
@@ -2101,10 +2107,18 @@
       <c r="F19" s="4"/>
     </row>
     <row r="20" spans="1:6" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A20" s="5"/>
-      <c r="B20" s="21"/>
-      <c r="C20" s="17"/>
-      <c r="D20" s="15"/>
+      <c r="A20" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" s="21">
+        <v>1</v>
+      </c>
+      <c r="C20" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="D20" s="15" t="s">
+        <v>44</v>
+      </c>
       <c r="E20" s="19"/>
       <c r="F20" s="4"/>
     </row>
@@ -2186,7 +2200,7 @@
       </c>
       <c r="B30" s="14">
         <f>SUMIF(E4:E28,"&lt;&gt;x",B4:B28)</f>
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>

--- a/DTT-Assessment-Hour-Log.xlsx
+++ b/DTT-Assessment-Hour-Log.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\dtt-frontend-assessment\dtt-frontend-assessment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CCB0B30-DE9E-451E-9F1B-54C054A04679}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43611521-7F1B-41C7-A00D-D8117F05B115}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="50" windowWidth="25600" windowHeight="15230" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="28800" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DTT Test Hour Log" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="55">
   <si>
     <t>Subject</t>
   </si>
@@ -188,6 +188,36 @@
   </si>
   <si>
     <t>Added edit and delete action buttons to HouseCard component that appear on hover. Buttons are only visible for owned listings using madeByMe property from the API. Used opacity transition for smooth hover effect. Delete emits event to parent, edit navigates to edit page</t>
+  </si>
+  <si>
+    <t>House detail page</t>
+  </si>
+  <si>
+    <t>26/05/2026</t>
+  </si>
+  <si>
+    <t>Built HouseDetailView with two column grid layout showing full house details including description, construction year and garage. Added delete confirmation modal. Edit and delete buttons visible only for owned listings using madeByMe property</t>
+  </si>
+  <si>
+    <t>RecommendedHouses component</t>
+  </si>
+  <si>
+    <t>Created reusable RecommendedHouses component used on the detail page. Implemented recommendation logic based on same city and similar price range within 50% of current price with fallback to any other houses</t>
+  </si>
+  <si>
+    <t>Router configuration</t>
+  </si>
+  <si>
+    <t>Added activeNav meta to all house routes so navbar correctly highlights Houses link when viewing detail, create and edit pages</t>
+  </si>
+  <si>
+    <t>Code cleanup</t>
+  </si>
+  <si>
+    <t>27/05/2026</t>
+  </si>
+  <si>
+    <t>Cleaned up comments and formatting across all components and files. Removed blank lines between JSDoc comments and functions, fixed comment wording, replaced hardcoded values with CSS variables</t>
   </si>
 </sst>
 </file>
@@ -1804,17 +1834,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F33"/>
-  <sheetFormatPr defaultColWidth="6.46484375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="6.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="24.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="10.6640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="24.69921875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="10.69921875" style="1" customWidth="1"/>
     <col min="3" max="3" width="8.59765625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="158.06640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="6.46484375" style="1" customWidth="1"/>
-    <col min="7" max="251" width="6.46484375" customWidth="1"/>
+    <col min="4" max="4" width="158.09765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="6.5" style="1" customWidth="1"/>
+    <col min="7" max="251" width="6.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="73.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" ht="73.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="22"/>
       <c r="B1" s="23"/>
       <c r="C1" s="23"/>
@@ -1822,7 +1852,7 @@
       <c r="E1" s="10"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="24" t="s">
         <v>6</v>
       </c>
@@ -1832,7 +1862,7 @@
       <c r="E2" s="24"/>
       <c r="F2" s="25"/>
     </row>
-    <row r="3" spans="1:6" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="16" t="s">
         <v>0</v>
       </c>
@@ -1850,7 +1880,7 @@
       </c>
       <c r="F3" s="4"/>
     </row>
-    <row r="4" spans="1:6" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>7</v>
       </c>
@@ -1866,7 +1896,7 @@
       <c r="E4" s="19"/>
       <c r="F4" s="4"/>
     </row>
-    <row r="5" spans="1:6" ht="18" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
         <v>9</v>
       </c>
@@ -1882,7 +1912,7 @@
       <c r="E5" s="19"/>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" spans="1:6" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="18" t="s">
         <v>12</v>
       </c>
@@ -1898,7 +1928,7 @@
       <c r="E6" s="19"/>
       <c r="F6" s="4"/>
     </row>
-    <row r="7" spans="1:6" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
         <v>14</v>
       </c>
@@ -1914,7 +1944,7 @@
       <c r="E7" s="19"/>
       <c r="F7" s="4"/>
     </row>
-    <row r="8" spans="1:6" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
         <v>16</v>
       </c>
@@ -1930,7 +1960,7 @@
       <c r="E8" s="19"/>
       <c r="F8" s="4"/>
     </row>
-    <row r="9" spans="1:6" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="5" t="s">
         <v>19</v>
       </c>
@@ -1946,7 +1976,7 @@
       <c r="E9" s="19"/>
       <c r="F9" s="4"/>
     </row>
-    <row r="10" spans="1:6" ht="18" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
         <v>16</v>
       </c>
@@ -1962,7 +1992,7 @@
       <c r="E10" s="19"/>
       <c r="F10" s="4"/>
     </row>
-    <row r="11" spans="1:6" ht="18" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
         <v>22</v>
       </c>
@@ -1978,7 +2008,7 @@
       <c r="E11" s="19"/>
       <c r="F11" s="4"/>
     </row>
-    <row r="12" spans="1:6" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
         <v>25</v>
       </c>
@@ -1994,7 +2024,7 @@
       <c r="E12" s="19"/>
       <c r="F12" s="4"/>
     </row>
-    <row r="13" spans="1:6" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="5" t="s">
         <v>26</v>
       </c>
@@ -2010,7 +2040,7 @@
       <c r="E13" s="19"/>
       <c r="F13" s="4"/>
     </row>
-    <row r="14" spans="1:6" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="5" t="s">
         <v>27</v>
       </c>
@@ -2026,7 +2056,7 @@
       <c r="E14" s="19"/>
       <c r="F14" s="4"/>
     </row>
-    <row r="15" spans="1:6" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="5" t="s">
         <v>32</v>
       </c>
@@ -2042,7 +2072,7 @@
       <c r="E15" s="19"/>
       <c r="F15" s="4"/>
     </row>
-    <row r="16" spans="1:6" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="5" t="s">
         <v>34</v>
       </c>
@@ -2058,7 +2088,7 @@
       <c r="E16" s="19"/>
       <c r="F16" s="4"/>
     </row>
-    <row r="17" spans="1:6" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="5" t="s">
         <v>36</v>
       </c>
@@ -2074,7 +2104,7 @@
       <c r="E17" s="19"/>
       <c r="F17" s="4"/>
     </row>
-    <row r="18" spans="1:6" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="5" t="s">
         <v>38</v>
       </c>
@@ -2090,7 +2120,7 @@
       <c r="E18" s="19"/>
       <c r="F18" s="4"/>
     </row>
-    <row r="19" spans="1:6" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="5" t="s">
         <v>41</v>
       </c>
@@ -2106,7 +2136,7 @@
       <c r="E19" s="19"/>
       <c r="F19" s="4"/>
     </row>
-    <row r="20" spans="1:6" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="5" t="s">
         <v>43</v>
       </c>
@@ -2122,39 +2152,71 @@
       <c r="E20" s="19"/>
       <c r="F20" s="4"/>
     </row>
-    <row r="21" spans="1:6" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A21" s="5"/>
-      <c r="B21" s="21"/>
-      <c r="C21" s="17"/>
-      <c r="D21" s="15"/>
+    <row r="21" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B21" s="21">
+        <v>2</v>
+      </c>
+      <c r="C21" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D21" s="15" t="s">
+        <v>47</v>
+      </c>
       <c r="E21" s="19"/>
       <c r="F21" s="4"/>
     </row>
-    <row r="22" spans="1:6" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A22" s="5"/>
-      <c r="B22" s="21"/>
-      <c r="C22" s="17"/>
-      <c r="D22" s="15"/>
+    <row r="22" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B22" s="21">
+        <v>1</v>
+      </c>
+      <c r="C22" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D22" s="15" t="s">
+        <v>49</v>
+      </c>
       <c r="E22" s="19"/>
       <c r="F22" s="4"/>
     </row>
-    <row r="23" spans="1:6" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A23" s="5"/>
-      <c r="B23" s="21"/>
-      <c r="C23" s="17"/>
-      <c r="D23" s="15"/>
+    <row r="23" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B23" s="21">
+        <v>0.5</v>
+      </c>
+      <c r="C23" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D23" s="15" t="s">
+        <v>51</v>
+      </c>
       <c r="E23" s="19"/>
       <c r="F23" s="4"/>
     </row>
-    <row r="24" spans="1:6" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A24" s="5"/>
-      <c r="B24" s="21"/>
-      <c r="C24" s="17"/>
-      <c r="D24" s="15"/>
+    <row r="24" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B24" s="21">
+        <v>1</v>
+      </c>
+      <c r="C24" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="D24" s="15" t="s">
+        <v>54</v>
+      </c>
       <c r="E24" s="19"/>
       <c r="F24" s="4"/>
     </row>
-    <row r="25" spans="1:6" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="25" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="5"/>
       <c r="B25" s="21"/>
       <c r="C25" s="17"/>
@@ -2162,7 +2224,7 @@
       <c r="E25" s="19"/>
       <c r="F25" s="4"/>
     </row>
-    <row r="26" spans="1:6" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="26" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="5"/>
       <c r="B26" s="21"/>
       <c r="C26" s="17"/>
@@ -2170,7 +2232,7 @@
       <c r="E26" s="19"/>
       <c r="F26" s="4"/>
     </row>
-    <row r="27" spans="1:6" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="27" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="5"/>
       <c r="B27" s="21"/>
       <c r="C27" s="17"/>
@@ -2178,7 +2240,7 @@
       <c r="E27" s="19"/>
       <c r="F27" s="4"/>
     </row>
-    <row r="28" spans="1:6" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="28" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="5"/>
       <c r="B28" s="21"/>
       <c r="C28" s="17"/>
@@ -2186,7 +2248,7 @@
       <c r="E28" s="19"/>
       <c r="F28" s="4"/>
     </row>
-    <row r="29" spans="1:6" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:6" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="11"/>
       <c r="B29" s="12"/>
       <c r="C29" s="12"/>
@@ -2194,20 +2256,20 @@
       <c r="E29" s="3"/>
       <c r="F29" s="4"/>
     </row>
-    <row r="30" spans="1:6" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:6" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="13" t="s">
         <v>4</v>
       </c>
       <c r="B30" s="14">
         <f>SUMIF(E4:E28,"&lt;&gt;x",B4:B28)</f>
-        <v>13.5</v>
+        <v>18</v>
       </c>
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
       <c r="E30" s="3"/>
       <c r="F30" s="4"/>
     </row>
-    <row r="31" spans="1:6" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="6"/>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
@@ -2215,7 +2277,7 @@
       <c r="E31" s="3"/>
       <c r="F31" s="4"/>
     </row>
-    <row r="32" spans="1:6" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:6" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6"/>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
@@ -2223,7 +2285,7 @@
       <c r="E32" s="3"/>
       <c r="F32" s="4"/>
     </row>
-    <row r="33" spans="1:6" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:6" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="7"/>
       <c r="B33" s="8"/>
       <c r="C33" s="8"/>

--- a/DTT-Assessment-Hour-Log.xlsx
+++ b/DTT-Assessment-Hour-Log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\dtt-frontend-assessment\dtt-frontend-assessment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43611521-7F1B-41C7-A00D-D8117F05B115}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF1475CE-3406-46F7-B8B5-439FE4D73E29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2340" yWindow="2340" windowWidth="28800" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="58">
   <si>
     <t>Subject</t>
   </si>
@@ -218,6 +218,15 @@
   </si>
   <si>
     <t>Cleaned up comments and formatting across all components and files. Removed blank lines between JSDoc comments and functions, fixed comment wording, replaced hardcoded values with CSS variables</t>
+  </si>
+  <si>
+    <t>Added /about route pointing to the AboutView component</t>
+  </si>
+  <si>
+    <t>About page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Built About page with information about DTT Real Estate and Design and Development section showing DTT branding and website link. </t>
   </si>
 </sst>
 </file>
@@ -2217,18 +2226,34 @@
       <c r="F24" s="4"/>
     </row>
     <row r="25" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="5"/>
-      <c r="B25" s="21"/>
-      <c r="C25" s="17"/>
-      <c r="D25" s="15"/>
+      <c r="A25" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B25" s="21">
+        <v>0.5</v>
+      </c>
+      <c r="C25" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="D25" s="15" t="s">
+        <v>55</v>
+      </c>
       <c r="E25" s="19"/>
       <c r="F25" s="4"/>
     </row>
     <row r="26" spans="1:6" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="5"/>
-      <c r="B26" s="21"/>
-      <c r="C26" s="17"/>
-      <c r="D26" s="15"/>
+      <c r="A26" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B26" s="21">
+        <v>1</v>
+      </c>
+      <c r="C26" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="D26" s="15" t="s">
+        <v>57</v>
+      </c>
       <c r="E26" s="19"/>
       <c r="F26" s="4"/>
     </row>
@@ -2262,7 +2287,7 @@
       </c>
       <c r="B30" s="14">
         <f>SUMIF(E4:E28,"&lt;&gt;x",B4:B28)</f>
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
